--- a/llm_labeling/code2text_python_rating.xlsx
+++ b/llm_labeling/code2text_python_rating.xlsx
@@ -510,7 +510,7 @@
         <v>0.9355779686079343</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
         <v>1.008166070895517</v>
@@ -549,7 +549,7 @@
         <v>1.007200515691478</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -588,7 +588,7 @@
         <v>0.9280379612394892</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>0.8593372714230572</v>
@@ -627,7 +627,7 @@
         <v>0.8035881040050555</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>1.650987722989433</v>
@@ -666,7 +666,7 @@
         <v>0.7465580872262197</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
         <v>1.062577052993187</v>
@@ -705,7 +705,7 @@
         <v>0.6872661189957208</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>1.20566018689926</v>
@@ -744,7 +744,7 @@
         <v>0.6955043614872732</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>1.315279920511133</v>
@@ -783,7 +783,7 @@
         <v>0.3552721923209445</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
         <v>2.50319294874323</v>
@@ -822,7 +822,7 @@
         <v>0.9216283858270756</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>0.8284204781041018</v>
@@ -861,7 +861,7 @@
         <v>0.9059732599740568</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>1.177658947627176</v>
@@ -900,7 +900,7 @@
         <v>0.9170126222558316</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0.3590524547360447</v>
@@ -939,7 +939,7 @@
         <v>0.6400204942641929</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
         <v>1.559584333403506</v>
@@ -978,7 +978,7 @@
         <v>1.302798802626917</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0.1310828260534545</v>
@@ -1017,7 +1017,7 @@
         <v>1.076215402714742</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0.450388625059611</v>
@@ -1056,7 +1056,7 @@
         <v>0.7464942484767676</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
         <v>1.077456194435146</v>
@@ -1095,7 +1095,7 @@
         <v>0.5697936236071852</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
         <v>1.656014595354423</v>
@@ -1134,7 +1134,7 @@
         <v>0.9881054343682446</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0.8211119422493731</v>
@@ -1173,7 +1173,7 @@
         <v>0.8051384213679031</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
         <v>0.8842147704847014</v>
@@ -1212,7 +1212,7 @@
         <v>0.9711673315527326</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>0.2883534452447986</v>
@@ -1251,7 +1251,7 @@
         <v>0.8437938048446951</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
         <v>0.9741696147001039</v>
@@ -1290,7 +1290,7 @@
         <v>0.8628233033391974</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
         <v>1.789856946466333</v>
@@ -1329,7 +1329,7 @@
         <v>0.6980982977874831</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
         <v>1.2824649352103</v>

--- a/llm_labeling/code2text_python_rating.xlsx
+++ b/llm_labeling/code2text_python_rating.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,20 +461,30 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>harmonic_mean</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>hm_rank</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>distance</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>distance_rank</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>regression_rank</t>
         </is>
@@ -507,15 +517,21 @@
         <v>0.2323800580776789</v>
       </c>
       <c r="H2" t="n">
+        <v>0.3099264130468212</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
         <v>0.9355779686079343</v>
       </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.008166070895517</v>
-      </c>
       <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.003874381006055</v>
+      </c>
+      <c r="M2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -546,15 +562,21 @@
         <v>0.8797798735270242</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>1.007200515691478</v>
       </c>
-      <c r="I3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -585,16 +607,22 @@
         <v>0.3210065954302572</v>
       </c>
       <c r="H4" t="n">
+        <v>0.3426263849048042</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
         <v>0.9280379612394892</v>
       </c>
-      <c r="I4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.8593372714230572</v>
-      </c>
       <c r="K4" t="n">
         <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8817416739893711</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -624,16 +652,22 @@
         <v>0.2326092858439093</v>
       </c>
       <c r="H5" t="n">
+        <v>0.3563670596363468</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
         <v>0.8035881040050555</v>
       </c>
-      <c r="I5" t="n">
-        <v>3</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.650987722989433</v>
-      </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.644210837232113</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -663,15 +697,21 @@
         <v>0.6159846744978743</v>
       </c>
       <c r="H6" t="n">
+        <v>0.4542470247533087</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
         <v>0.7465580872262197</v>
       </c>
-      <c r="I6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.062577052993187</v>
-      </c>
       <c r="K6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.9523526875478309</v>
+      </c>
+      <c r="M6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -702,15 +742,21 @@
         <v>0.7607500750351736</v>
       </c>
       <c r="H7" t="n">
+        <v>0.4847689860796955</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
         <v>0.6872661189957208</v>
       </c>
-      <c r="I7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.20566018689926</v>
-      </c>
       <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.9809904304083121</v>
+      </c>
+      <c r="M7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -741,15 +787,21 @@
         <v>0.9043107608230538</v>
       </c>
       <c r="H8" t="n">
+        <v>0.4629506225903163</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
         <v>0.6955043614872732</v>
       </c>
-      <c r="I8" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.315279920511133</v>
-      </c>
       <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.93430972832243</v>
+      </c>
+      <c r="M8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -780,15 +832,21 @@
         <v>0.8121002489914432</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3552721923209445</v>
+        <v>0.7510192784643605</v>
       </c>
       <c r="I9" t="n">
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>2.50319294874323</v>
+        <v>0.3552721923209445</v>
       </c>
       <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.959972026988585</v>
+      </c>
+      <c r="M9" t="n">
         <v>5</v>
       </c>
     </row>
@@ -819,16 +877,22 @@
         <v>0.349707531720082</v>
       </c>
       <c r="H10" t="n">
+        <v>0.3483062204725147</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
         <v>0.9216283858270756</v>
       </c>
-      <c r="I10" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.8284204781041018</v>
-      </c>
       <c r="K10" t="n">
         <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.8473681571775021</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -858,15 +922,21 @@
         <v>0.2073018638511295</v>
       </c>
       <c r="H11" t="n">
+        <v>0.3027864516913082</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
         <v>0.9059732599740568</v>
       </c>
-      <c r="I11" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.177658947627176</v>
-      </c>
       <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.151529967425046</v>
+      </c>
+      <c r="M11" t="n">
         <v>3</v>
       </c>
     </row>
@@ -897,15 +967,21 @@
         <v>0.8606067947590625</v>
       </c>
       <c r="H12" t="n">
+        <v>0.168908332021529</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
         <v>0.9170126222558316</v>
       </c>
-      <c r="I12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.3590524547360447</v>
-      </c>
       <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2697424926103975</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -936,16 +1012,22 @@
         <v>0.906105735452531</v>
       </c>
       <c r="H13" t="n">
+        <v>0.522311866429213</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="n">
         <v>0.6400204942641929</v>
       </c>
-      <c r="I13" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.559584333403506</v>
-      </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.104381425337355</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -975,15 +1057,21 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
         <v>1.302798802626917</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>1</v>
       </c>
-      <c r="J14" t="n">
-        <v>0.1310828260534545</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
+        <v>0.1447625417078079</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1014,16 +1102,22 @@
         <v>0.2820073181519435</v>
       </c>
       <c r="H15" t="n">
+        <v>0.2328580781435386</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="n">
         <v>1.076215402714742</v>
       </c>
-      <c r="I15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.450388625059611</v>
-      </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.45959505897699</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1053,15 +1147,21 @@
         <v>0.599121015100532</v>
       </c>
       <c r="H16" t="n">
+        <v>0.4576884350976886</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
         <v>0.7464942484767676</v>
       </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.077456194435146</v>
-      </c>
       <c r="K16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.975222534556021</v>
+      </c>
+      <c r="M16" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1092,15 +1192,21 @@
         <v>0.6787716699231076</v>
       </c>
       <c r="H17" t="n">
+        <v>0.5948435236513213</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
         <v>0.5697936236071852</v>
       </c>
-      <c r="I17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.656014595354423</v>
-      </c>
       <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.427185858173753</v>
+      </c>
+      <c r="M17" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1131,16 +1237,22 @@
         <v>0.2310951685282521</v>
       </c>
       <c r="H18" t="n">
+        <v>0.2872356086374091</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
         <v>0.9881054343682446</v>
       </c>
-      <c r="I18" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.8211119422493731</v>
-      </c>
       <c r="K18" t="n">
         <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.8169119928287266</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1170,16 +1282,22 @@
         <v>0.5924175292477878</v>
       </c>
       <c r="H19" t="n">
+        <v>0.4032474457167016</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
         <v>0.8051384213679031</v>
       </c>
-      <c r="I19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.8842147704847014</v>
-      </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.8033983117140643</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1209,15 +1327,21 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
+        <v>0.05604928640297197</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
         <v>0.9711673315527326</v>
       </c>
-      <c r="I20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.2883534452447986</v>
-      </c>
       <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.1106821983738362</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1248,16 +1372,22 @@
         <v>0.4196590333781476</v>
       </c>
       <c r="H21" t="n">
+        <v>0.4029229412079998</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
         <v>0.8437938048446951</v>
       </c>
-      <c r="I21" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.9741696147001039</v>
-      </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.9717282534977015</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1287,16 +1417,22 @@
         <v>0.1371766966608026</v>
       </c>
       <c r="H22" t="n">
+        <v>0.2412583674350824</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
         <v>0.8628233033391974</v>
       </c>
-      <c r="I22" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1.789856946466333</v>
-      </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.67210774604849</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -1326,16 +1462,22 @@
         <v>0.5653415401383384</v>
       </c>
       <c r="H23" t="n">
+        <v>0.5034224469967478</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
         <v>0.6980982977874831</v>
       </c>
-      <c r="I23" t="n">
-        <v>3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1.2824649352103</v>
-      </c>
       <c r="K23" t="n">
         <v>3</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.183158206184563</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
